--- a/pipelines/Demo_data/Output_data/group_export/Отчёт_Юг_2025-Q1.xlsx
+++ b/pipelines/Demo_data/Output_data/group_export/Отчёт_Юг_2025-Q1.xlsx
@@ -101,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -126,6 +126,7 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -133,6 +134,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -428,11 +430,11 @@
   <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="22.00390625" customWidth="1" style="13" min="1" max="1"/>
-    <col width="19.140625" customWidth="1" style="13" min="2" max="2"/>
-    <col width="34.421875" customWidth="1" style="13" min="3" max="3"/>
-    <col width="18.7109375" customWidth="1" style="13" min="4" max="4"/>
-    <col width="14.57421875" customWidth="1" style="13" min="5" max="5"/>
+    <col width="22.00390625" customWidth="1" style="14" min="1" max="1"/>
+    <col width="19.140625" customWidth="1" style="14" min="2" max="2"/>
+    <col width="34.421875" customWidth="1" style="14" min="3" max="3"/>
+    <col width="18.7109375" customWidth="1" style="14" min="4" max="4"/>
+    <col width="14.57421875" customWidth="1" style="14" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -446,7 +448,7 @@
           <t xml:space="preserve"> Создан</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>02.06.2026</t>
         </is>
@@ -468,7 +470,7 @@
     <row r="4"/>
     <row r="5"/>
     <row r="6"/>
-    <row r="7" ht="14.25" customHeight="1" s="13">
+    <row r="7" ht="14.25" customHeight="1" s="14">
       <c r="A7" s="3" t="n">
         <v>1</v>
       </c>
@@ -480,10 +482,10 @@
       <c r="C7" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="16" t="n">
         <v>213.33</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>2222.33</v>
       </c>
       <c r="F7" t="inlineStr">
@@ -519,7 +521,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="14.25" customHeight="1" s="13">
+    <row r="9" ht="14.25" customHeight="1" s="14">
       <c r="A9" s="3" t="n">
         <v>1</v>
       </c>
@@ -531,19 +533,19 @@
       <c r="C9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>200</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>&lt;- Для табличного вывода можно применять плайсхолдеры , но в настройках вывода таблицы, все равно нужно явно кузывать номер столбца для вывода</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="14.25" customHeight="1" s="13">
+          <t>&lt;- Для табличного вывода можно применять плайсхолдеры , но в настройках вывода таблицы, все равно нужно явно указывать номер столбца для вывода</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1" s="14">
       <c r="A10" s="3" t="n">
         <v>2</v>
       </c>
@@ -555,14 +557,14 @@
       <c r="C10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="16" t="n">
         <v>60</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="11" ht="14.25" customHeight="1" s="13">
+    <row r="11" ht="14.25" customHeight="1" s="14">
       <c r="A11" s="3" t="n">
         <v>3</v>
       </c>
@@ -574,10 +576,10 @@
       <c r="C11" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="16" t="n">
         <v>35</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>140</v>
       </c>
     </row>
@@ -598,7 +600,7 @@
           <t>Итого сумма:</t>
         </is>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="18" t="n">
         <v>400</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -610,15 +612,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" ht="14.25" customHeight="1" s="13"/>
-    <row r="14"/>
+    <row r="13" ht="14.25" customHeight="1" s="14"/>
+    <row r="14" ht="14.25" customHeight="1" s="14"/>
     <row r="15">
-      <c r="A15" s="17" t="n"/>
-    </row>
-    <row r="16" ht="14.25" customHeight="1" s="13"/>
+      <c r="A15" s="19" t="n"/>
+    </row>
+    <row r="16" ht="14.25" customHeight="1" s="14">
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Список лотов поставки: 3 ; 4 ; 5</t>
+        </is>
+      </c>
+    </row>
     <row r="17"/>
     <row r="18">
-      <c r="E18" s="17" t="n"/>
+      <c r="E18" s="19" t="n"/>
     </row>
     <row r="19"/>
     <row r="20"/>
@@ -628,18 +636,12 @@
     <row r="24"/>
     <row r="25"/>
     <row r="26"/>
-    <row r="27" ht="14.25" customHeight="1" s="13"/>
+    <row r="27" ht="14.25" customHeight="1" s="14"/>
     <row r="28"/>
-    <row r="29">
-      <c r="I29" s="11" t="inlineStr">
-        <is>
-          <t>Итого кол-во: 10.0</t>
-        </is>
-      </c>
-    </row>
+    <row r="29"/>
     <row r="30"/>
     <row r="31"/>
-    <row r="32" ht="14.25" customHeight="1" s="13"/>
+    <row r="32" ht="14.25" customHeight="1" s="14"/>
     <row r="33"/>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">

--- a/pipelines/Demo_data/Output_data/group_export/Отчёт_Юг_2025-Q1.xlsx
+++ b/pipelines/Demo_data/Output_data/group_export/Отчёт_Юг_2025-Q1.xlsx
@@ -450,7 +450,7 @@
       </c>
       <c r="C1" s="15" t="inlineStr">
         <is>
-          <t>02.06.2026</t>
+          <t>09.06.2026</t>
         </is>
       </c>
     </row>

--- a/pipelines/Demo_data/Output_data/group_export/Отчёт_Юг_2025-Q1.xlsx
+++ b/pipelines/Demo_data/Output_data/group_export/Отчёт_Юг_2025-Q1.xlsx
@@ -450,7 +450,7 @@
       </c>
       <c r="C1" s="15" t="inlineStr">
         <is>
-          <t>09.06.2026</t>
+          <t>10.06.2026</t>
         </is>
       </c>
     </row>

--- a/pipelines/Demo_data/Output_data/group_export/Отчёт_Юг_2025-Q1.xlsx
+++ b/pipelines/Demo_data/Output_data/group_export/Отчёт_Юг_2025-Q1.xlsx
@@ -101,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,11 +129,22 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -450,17 +461,17 @@
       </c>
       <c r="C1" s="15" t="inlineStr">
         <is>
-          <t>10.06.2026</t>
+          <t>14.06.2026</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Группа: Юг</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>Период: 2025-Q1</t>
         </is>
@@ -525,19 +536,25 @@
       <c r="A9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>Апельсин</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <v>40</v>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>200</v>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -549,48 +566,60 @@
       <c r="A10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>Мандарин</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>60</v>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1" s="14">
       <c r="A11" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Лимон</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>35</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>140</v>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>Строк: 3.0</t>
         </is>
       </c>
       <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>Итого кол-во: 10.0</t>
         </is>
@@ -600,7 +629,7 @@
           <t>Итого сумма:</t>
         </is>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="23" t="n">
         <v>400</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -615,10 +644,10 @@
     <row r="13" ht="14.25" customHeight="1" s="14"/>
     <row r="14" ht="14.25" customHeight="1" s="14"/>
     <row r="15">
-      <c r="A15" s="19" t="n"/>
+      <c r="A15" s="24" t="n"/>
     </row>
     <row r="16" ht="14.25" customHeight="1" s="14">
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>Список лотов поставки: 3 ; 4 ; 5</t>
         </is>
@@ -626,7 +655,7 @@
     </row>
     <row r="17"/>
     <row r="18">
-      <c r="E18" s="19" t="n"/>
+      <c r="E18" s="24" t="n"/>
     </row>
     <row r="19"/>
     <row r="20"/>
@@ -644,7 +673,7 @@
     <row r="32" ht="14.25" customHeight="1" s="14"/>
     <row r="33"/>
     <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>Итого кол-во: 10.0</t>
         </is>

--- a/pipelines/Demo_data/Output_data/group_export/Отчёт_Юг_2025-Q1.xlsx
+++ b/pipelines/Demo_data/Output_data/group_export/Отчёт_Юг_2025-Q1.xlsx
@@ -221,6 +221,711 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:r>
+              <a:t/>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <layout/>
+      <overlay val="0"/>
+      <spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" cap="all">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr/>
+        </a:p>
+      </txPr>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.22264"/>
+          <y val="0.06993000000000001"/>
+          <w val="0.43007"/>
+          <h val="0.71879"/>
+        </manualLayout>
+      </layout>
+      <pie3DChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Sheet1!$D$9:$D$10</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:alpha val="70000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:alpha val="70000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:alpha val="70000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:alpha val="70000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:alpha val="70000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="5"/>
+            <spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:alpha val="70000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="6"/>
+            <spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:alpha val="70000"/>
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dLbls>
+            <dLbl>
+              <idx val="0"/>
+              <spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <avLst/>
+                </a:prstGeom>
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:alpha val="90000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:prstDash val="solid"/>
+                  <a:round/>
+                </a:ln>
+              </spPr>
+              <txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38099" tIns="19049" rIns="38099" bIns="19049" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" i="0" strike="noStrike">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr/>
+                </a:p>
+              </txPr>
+              <dLblPos val="inEnd"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="1"/>
+              <showSerName val="0"/>
+              <showPercent val="0"/>
+              <showBubbleSize val="0"/>
+            </dLbl>
+            <dLbl>
+              <idx val="1"/>
+              <spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <avLst/>
+                </a:prstGeom>
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:alpha val="90000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:prstDash val="solid"/>
+                  <a:round/>
+                </a:ln>
+              </spPr>
+              <txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38099" tIns="19049" rIns="38099" bIns="19049" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" i="0" strike="noStrike">
+                      <a:solidFill>
+                        <a:schemeClr val="accent2"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr/>
+                </a:p>
+              </txPr>
+              <dLblPos val="inEnd"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="1"/>
+              <showSerName val="0"/>
+              <showPercent val="0"/>
+              <showBubbleSize val="0"/>
+            </dLbl>
+            <dLbl>
+              <idx val="2"/>
+              <spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <avLst/>
+                </a:prstGeom>
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:alpha val="90000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:prstDash val="solid"/>
+                  <a:round/>
+                </a:ln>
+              </spPr>
+              <txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38099" tIns="19049" rIns="38099" bIns="19049" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" i="0" strike="noStrike">
+                      <a:solidFill>
+                        <a:schemeClr val="accent3"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr/>
+                </a:p>
+              </txPr>
+              <dLblPos val="inEnd"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="1"/>
+              <showSerName val="0"/>
+              <showPercent val="0"/>
+              <showBubbleSize val="0"/>
+            </dLbl>
+            <dLbl>
+              <idx val="3"/>
+              <spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <avLst/>
+                </a:prstGeom>
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:alpha val="90000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:prstDash val="solid"/>
+                  <a:round/>
+                </a:ln>
+              </spPr>
+              <txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38099" tIns="19049" rIns="38099" bIns="19049" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" i="0" strike="noStrike">
+                      <a:solidFill>
+                        <a:schemeClr val="accent4"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr/>
+                </a:p>
+              </txPr>
+              <dLblPos val="inEnd"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="1"/>
+              <showSerName val="0"/>
+              <showPercent val="0"/>
+              <showBubbleSize val="0"/>
+            </dLbl>
+            <dLbl>
+              <idx val="4"/>
+              <spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <avLst/>
+                </a:prstGeom>
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:alpha val="90000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:prstDash val="solid"/>
+                  <a:round/>
+                </a:ln>
+              </spPr>
+              <txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38099" tIns="19049" rIns="38099" bIns="19049" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" i="0" strike="noStrike">
+                      <a:solidFill>
+                        <a:schemeClr val="accent5"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr/>
+                </a:p>
+              </txPr>
+              <dLblPos val="inEnd"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="1"/>
+              <showSerName val="0"/>
+              <showPercent val="0"/>
+              <showBubbleSize val="0"/>
+            </dLbl>
+            <dLbl>
+              <idx val="5"/>
+              <spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <avLst/>
+                </a:prstGeom>
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:alpha val="90000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:prstDash val="solid"/>
+                  <a:round/>
+                </a:ln>
+              </spPr>
+              <txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38099" tIns="19049" rIns="38099" bIns="19049" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" i="0" strike="noStrike">
+                      <a:solidFill>
+                        <a:schemeClr val="accent6"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr/>
+                </a:p>
+              </txPr>
+              <dLblPos val="inEnd"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="1"/>
+              <showSerName val="0"/>
+              <showPercent val="0"/>
+              <showBubbleSize val="0"/>
+            </dLbl>
+            <dLbl>
+              <idx val="6"/>
+              <spPr bwMode="auto">
+                <a:prstGeom prst="rect">
+                  <avLst/>
+                </a:prstGeom>
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:alpha val="90000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:prstDash val="solid"/>
+                  <a:round/>
+                </a:ln>
+              </spPr>
+              <txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38099" tIns="19049" rIns="38099" bIns="19049" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" i="0" strike="noStrike">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1">
+                          <a:lumMod val="60000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr/>
+                </a:p>
+              </txPr>
+              <dLblPos val="inEnd"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="1"/>
+              <showSerName val="0"/>
+              <showPercent val="0"/>
+              <showBubbleSize val="0"/>
+            </dLbl>
+            <spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:alpha val="90000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+                <a:round/>
+              </a:ln>
+            </spPr>
+            <txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38099" tIns="19049" rIns="38099" bIns="19049" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" strike="noStrike">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr/>
+              </a:p>
+            </txPr>
+            <dLblPos val="inEnd"/>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="1"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+            <showLeaderLines val="1"/>
+          </dLbls>
+          <cat>
+            <strRef>
+              <f>Sheet1!$B$9:$B$18</f>
+            </strRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Sheet1!$D$11:$D$17</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="90000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+          </spPr>
+          <txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38099" tIns="19049" rIns="38099" bIns="19049" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" strike="noStrike">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+              <a:endParaRPr/>
+            </a:p>
+          </txPr>
+          <dLblPos val="inEnd"/>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="1"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+          <showLeaderLines val="1"/>
+        </dLbls>
+      </pie3DChart>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr bwMode="auto">
+    <a:xfrm>
+      <a:off x="6496049" y="3081337"/>
+      <a:ext cx="4552949" cy="2724149"/>
+    </a:xfrm>
+    <a:prstGeom prst="rect">
+      <avLst/>
+    </a:prstGeom>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+      <a:round/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>4</col>
+      <colOff>209549</colOff>
+      <row>17</row>
+      <rowOff>4762</rowOff>
+    </from>
+    <to>
+      <col>11</col>
+      <colOff>133349</colOff>
+      <row>32</row>
+      <rowOff>14287</rowOff>
+    </to>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -683,5 +1388,6 @@
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" useFirstPageNumber="0" pageOrder="downThenOver" usePrinterDefaults="1" blackAndWhite="0" draft="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>